--- a/travel_consent_forms/032_international_travel_participant_agreement--travel_consent_forms.xlsx
+++ b/travel_consent_forms/032_international_travel_participant_agreement--travel_consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -692,7 +692,7 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>emergency_contact_permission</t>
+          <t>participant_consent</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Emergency Contact Permission</t>
+          <t>Participant Consent</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>participant_consent</t>
+          <t>school_permission</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Participant Consent</t>
+          <t>School Permission</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>school_permission_prophets</t>
+          <t>travel_supervisors</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>School Permission</t>
+          <t>Travel Supervisors</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,41 +865,41 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>school_permission</t>
+          <t>participant_consent_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>School Permission</t>
+          <t>Participant Consent 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>travel_supervisors</t>
+          <t>school_permission_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Travel Supervisors</t>
+          <t>School Permission 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -911,177 +911,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>school_permission_2</t>
+          <t>participant_consent_3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>School Permission</t>
+          <t>Participant Consent 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>travel_supervisors_2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Travel Supervisors</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>school_permission_3</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>School Permission</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>travel_supervisors_3</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Travel Supervisors</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>travel_supervisors_4</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Travel Supervisors</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>school_permission_4</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>School Permission</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>school_permission_5</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>School Permission</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>school_permission_6</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>School Permission</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,7 +937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1131,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>mom</t>
+          <t>child</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Mom</t>
+          <t>Child</t>
         </is>
       </c>
     </row>
@@ -1148,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>dad</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dad</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>brother</t>
+          <t>sponsor</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Sponsor</t>
         </is>
       </c>
     </row>
@@ -1182,46 +1021,46 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>sister</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>emergency_contact_relationship_choices</t>
+          <t>travel_destination_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>friend</t>
+          <t>paris</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Friend</t>
+          <t>Paris</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>emergency_contact_relationship_choices</t>
+          <t>travel_destination_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>london</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>London</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>paris</t>
+          <t>rome</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Rome</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1089,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>london</t>
+          <t>barcelona</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Barcelona</t>
         </is>
       </c>
     </row>
@@ -1267,556 +1106,284 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>rome</t>
+          <t>new_york</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>New York</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>travel_destination_choices</t>
+          <t>participant_agreement_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>i_agree</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>I agree</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>travel_destination_choices</t>
+          <t>participant_agreement_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>new_york</t>
+          <t>i_do_not_agree</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>I do not agree</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>participant_agreement_choices</t>
+          <t>participant_consent_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>i_agree</t>
+          <t>i_consent</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>I agree</t>
+          <t>I consent</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>participant_agreement_choices</t>
+          <t>participant_consent_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>i_do_not_agree</t>
+          <t>i_do_not_consent</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>I do not agree</t>
+          <t>I do not consent</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>emergency_contact_permission_choices</t>
+          <t>school_permission_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>emergency_contact_permission_choices</t>
+          <t>school_permission_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>participant_consent_choices</t>
+          <t>travel_supervisors_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>i_consent</t>
+          <t>teacher</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>I consent</t>
+          <t>Teacher</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>participant_consent_choices</t>
+          <t>travel_supervisors_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>i_do_not_consent</t>
+          <t>school_administrator</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>I do not consent</t>
+          <t>School Administrator</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>school_permission_prophets_choices</t>
+          <t>travel_supervisors_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>group_leader</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Group Leader</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>school_permission_prophets_choices</t>
+          <t>travel_supervisors_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>school_permission_choices</t>
+          <t>participant_consent_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>i_consent</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>I consent</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>school_permission_choices</t>
+          <t>participant_consent_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>i_do_not_consent</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>I do not consent</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>travel_supervisors_choices</t>
+          <t>school_permission_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>teacher</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Teacher</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>travel_supervisors_choices</t>
+          <t>school_permission_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>school_administrator</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>School Administrator</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>travel_supervisors_choices</t>
+          <t>participant_consent_3_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>group_leader</t>
+          <t>i_consent</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Group Leader</t>
+          <t>I consent</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>travel_supervisors_choices</t>
+          <t>participant_consent_3_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>i_do_not_consent</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>school_permission_2_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>school_permission_2_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>travel_supervisors_2_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>travel_supervisors_2_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>school_permission_3_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>school_permission_3_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>travel_supervisors_3_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>travel_supervisors_3_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>travel_supervisors_4_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>travel_supervisors_4_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>school_permission_4_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>school_permission_4_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>school_permission_5_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>school_permission_5_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>school_permission_6_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>school_permission_6_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>I do not consent</t>
         </is>
       </c>
     </row>
